--- a/exports/report_assignment2.xlsx
+++ b/exports/report_assignment2.xlsx
@@ -37,12 +37,18 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFD966"/>
+        <bgColor rgb="00FFD966"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -63,12 +69,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -437,14 +446,18 @@
   </sheetPr>
   <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>revenue</t>
         </is>
@@ -596,14 +609,18 @@
   </sheetPr>
   <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>customer_state</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>avg_order_value</t>
         </is>
@@ -785,21 +802,25 @@
   </sheetPr>
   <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>month</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>revenue</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="4" t="n">
         <v>42614</v>
       </c>
       <c r="B2" t="n">
@@ -807,7 +828,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="4" t="n">
         <v>42644</v>
       </c>
       <c r="B3" t="n">
@@ -815,7 +836,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="4" t="n">
         <v>42705</v>
       </c>
       <c r="B4" t="n">
@@ -823,7 +844,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="4" t="n">
         <v>42736</v>
       </c>
       <c r="B5" t="n">
@@ -831,7 +852,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="4" t="n">
         <v>42767</v>
       </c>
       <c r="B6" t="n">
@@ -839,7 +860,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="4" t="n">
         <v>42795</v>
       </c>
       <c r="B7" t="n">
@@ -847,7 +868,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="4" t="n">
         <v>42826</v>
       </c>
       <c r="B8" t="n">
@@ -855,7 +876,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="4" t="n">
         <v>42856</v>
       </c>
       <c r="B9" t="n">
@@ -863,7 +884,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="4" t="n">
         <v>42887</v>
       </c>
       <c r="B10" t="n">
@@ -871,7 +892,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="4" t="n">
         <v>42917</v>
       </c>
       <c r="B11" t="n">
@@ -879,7 +900,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="4" t="n">
         <v>42948</v>
       </c>
       <c r="B12" t="n">
@@ -887,7 +908,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="4" t="n">
         <v>42979</v>
       </c>
       <c r="B13" t="n">
@@ -895,7 +916,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="4" t="n">
         <v>43009</v>
       </c>
       <c r="B14" t="n">
@@ -903,7 +924,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="4" t="n">
         <v>43040</v>
       </c>
       <c r="B15" t="n">
@@ -911,7 +932,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="4" t="n">
         <v>43070</v>
       </c>
       <c r="B16" t="n">
@@ -919,7 +940,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="4" t="n">
         <v>43101</v>
       </c>
       <c r="B17" t="n">
@@ -927,7 +948,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="4" t="n">
         <v>43132</v>
       </c>
       <c r="B18" t="n">
@@ -935,7 +956,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="4" t="n">
         <v>43160</v>
       </c>
       <c r="B19" t="n">
@@ -943,7 +964,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="4" t="n">
         <v>43191</v>
       </c>
       <c r="B20" t="n">
@@ -951,7 +972,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="4" t="n">
         <v>43221</v>
       </c>
       <c r="B21" t="n">
@@ -959,7 +980,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="4" t="n">
         <v>43252</v>
       </c>
       <c r="B22" t="n">
@@ -967,7 +988,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="4" t="n">
         <v>43282</v>
       </c>
       <c r="B23" t="n">
@@ -975,7 +996,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="4" t="n">
         <v>43313</v>
       </c>
       <c r="B24" t="n">
@@ -983,7 +1004,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="4" t="n">
         <v>43344</v>
       </c>
       <c r="B25" t="n">
